--- a/batteries.xlsx
+++ b/batteries.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\technicien_knx\Documents\Antoine_Collignon\Simulateur\Application\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4E028CCC-0731-4A94-86B8-BF5E1AF4AB59}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6BB34F87-5EE5-4CE6-BB46-8337FE01568B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{439F2F0B-EBB6-48D7-BDE1-24F1D6BB5D52}"/>
+    <workbookView xWindow="28680" yWindow="165" windowWidth="29040" windowHeight="15720" xr2:uid="{439F2F0B-EBB6-48D7-BDE1-24F1D6BB5D52}"/>
   </bookViews>
   <sheets>
     <sheet name="Batt" sheetId="3" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="148" uniqueCount="55">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="85" uniqueCount="42">
   <si>
     <t>Marque</t>
   </si>
@@ -48,18 +48,6 @@
     <t>Référence</t>
   </si>
   <si>
-    <t>Type</t>
-  </si>
-  <si>
-    <t>Haute tension DC</t>
-  </si>
-  <si>
-    <t>Type de cellules</t>
-  </si>
-  <si>
-    <t>LFP (Lithium)</t>
-  </si>
-  <si>
     <t>Energie nom totale (kWh)</t>
   </si>
   <si>
@@ -102,30 +90,6 @@
     <t>Huawei</t>
   </si>
   <si>
-    <t>LUNA2000-7-E1</t>
-  </si>
-  <si>
-    <t>LUNA2000-5-E1</t>
-  </si>
-  <si>
-    <t>LUNA2000-10-S1</t>
-  </si>
-  <si>
-    <t>LUNA2000-12-S1</t>
-  </si>
-  <si>
-    <t>LUNA2000-14-S1</t>
-  </si>
-  <si>
-    <t>LUNA2000-15-S1</t>
-  </si>
-  <si>
-    <t>LUNA2000-17-S1</t>
-  </si>
-  <si>
-    <t>LUNA2000-21-S1</t>
-  </si>
-  <si>
     <t>SMA Home 3.2</t>
   </si>
   <si>
@@ -159,9 +123,6 @@
     <t>Plu-Tri 9,6</t>
   </si>
   <si>
-    <t>LUNA2000-5-E1 (2x)</t>
-  </si>
-  <si>
     <t>LUNA2000-7-S1</t>
   </si>
   <si>
@@ -198,10 +159,10 @@
     <t>Energie util (kWh)</t>
   </si>
   <si>
-    <t>Colonne1</t>
-  </si>
-  <si>
-    <t>Huawei ok</t>
+    <t>Capacité commerciale (kWh)</t>
+  </si>
+  <si>
+    <t>Rendement</t>
   </si>
 </sst>
 </file>
@@ -271,20 +232,19 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{A4FAAE99-37F8-43E5-8DC6-4960C0E60F31}" name="Tableau13" displayName="Tableau13" ref="A1:H37" totalsRowShown="0">
-  <autoFilter ref="A1:H37" xr:uid="{EE3ACE20-211D-4EE0-86F4-04F562BCD3BD}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:G34">
-    <sortCondition ref="A1:A37"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{A4FAAE99-37F8-43E5-8DC6-4960C0E60F31}" name="Tableau13" displayName="Tableau13" ref="A1:G28" totalsRowShown="0">
+  <autoFilter ref="A1:G28" xr:uid="{EE3ACE20-211D-4EE0-86F4-04F562BCD3BD}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:E25">
+    <sortCondition ref="A1:A28"/>
   </sortState>
-  <tableColumns count="8">
+  <tableColumns count="7">
     <tableColumn id="2" xr3:uid="{C4C0F608-FE03-493E-A86D-689702E81FBD}" name="Marque"/>
     <tableColumn id="13" xr3:uid="{09B7C27F-7FA5-43FC-89CE-74D3FFD77488}" name="Référence"/>
-    <tableColumn id="16" xr3:uid="{2FDE3BDF-E47B-4AFE-96AF-4CAD946DC5D9}" name="Type"/>
-    <tableColumn id="15" xr3:uid="{445E6F1E-0388-4585-84CF-A15ED7837ABF}" name="Type de cellules"/>
     <tableColumn id="14" xr3:uid="{E91ECB42-E558-46DE-BCEB-7E0119220A6E}" name="Energie nom totale (kWh)"/>
     <tableColumn id="3" xr3:uid="{B731C204-3F0B-4D29-A459-22C74B3F60C4}" name="Energie util"/>
     <tableColumn id="1" xr3:uid="{E832FB0C-C0CA-45EB-8A35-2D325BD490D9}" name="P charge / décharge" dataDxfId="1"/>
-    <tableColumn id="4" xr3:uid="{B0AC4995-B96A-4BF2-A895-7694B8EC2EC7}" name="Colonne1"/>
+    <tableColumn id="4" xr3:uid="{B0AC4995-B96A-4BF2-A895-7694B8EC2EC7}" name="Rendement"/>
+    <tableColumn id="5" xr3:uid="{434E261B-B365-42B0-86E0-BF4AAA36F101}" name="Capacité commerciale (kWh)"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium14" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -624,19 +584,19 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{38952B00-7C12-4340-981B-DAC64C55AA63}">
-  <dimension ref="A1:H32"/>
+  <dimension ref="A1:G23"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="22.5703125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="54.7109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="5.5703125" customWidth="1"/>
-    <col min="4" max="4" width="10.7109375" customWidth="1"/>
-    <col min="5" max="5" width="26.42578125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="13.5703125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="24.42578125" customWidth="1"/>
+    <col min="2" max="2" width="42.140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="26.42578125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.5703125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="20.85546875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="13.85546875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="29.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -647,723 +607,501 @@
         <v>3</v>
       </c>
       <c r="D1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E1" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="F1" t="s">
-        <v>8</v>
+        <v>41</v>
       </c>
       <c r="G1" t="s">
-        <v>14</v>
-      </c>
-      <c r="H1" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>12</v>
-      </c>
-      <c r="C2" t="s">
-        <v>4</v>
-      </c>
-      <c r="D2" t="s">
-        <v>6</v>
+        <v>8</v>
+      </c>
+      <c r="C2">
+        <v>6.43</v>
+      </c>
+      <c r="D2">
+        <v>6.43</v>
       </c>
       <c r="E2">
-        <v>6.43</v>
-      </c>
-      <c r="F2">
-        <v>6.43</v>
-      </c>
-      <c r="G2">
         <f>35*115.2/1000</f>
         <v>4.032</v>
       </c>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="G2">
+        <v>6.4</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="B3" t="s">
-        <v>16</v>
-      </c>
-      <c r="C3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C3">
+        <v>3.98</v>
+      </c>
+      <c r="D3">
+        <v>3.98</v>
+      </c>
+      <c r="G3">
         <v>4</v>
       </c>
-      <c r="D3" t="s">
-        <v>6</v>
-      </c>
-      <c r="E3">
-        <v>3.98</v>
-      </c>
-      <c r="F3">
-        <v>3.98</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="B4" t="s">
-        <v>17</v>
-      </c>
-      <c r="C4" t="s">
-        <v>4</v>
-      </c>
-      <c r="D4" t="s">
-        <v>6</v>
-      </c>
-      <c r="E4">
+        <v>13</v>
+      </c>
+      <c r="C4">
         <v>11.9</v>
       </c>
-      <c r="F4">
+      <c r="D4">
         <f>Tableau13[[#This Row],[Energie nom totale (kWh)]]</f>
         <v>11.9</v>
       </c>
-      <c r="G4">
+      <c r="E4">
         <f>50*212.52/1000</f>
         <v>10.625999999999999</v>
       </c>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="G4">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="B5" t="s">
-        <v>18</v>
-      </c>
-      <c r="C5" t="s">
-        <v>4</v>
-      </c>
-      <c r="D5" t="s">
-        <v>6</v>
-      </c>
-      <c r="E5">
+        <v>14</v>
+      </c>
+      <c r="C5">
         <v>15.9</v>
       </c>
-      <c r="F5">
+      <c r="D5">
         <f>Tableau13[[#This Row],[Energie nom totale (kWh)]]</f>
         <v>15.9</v>
       </c>
-      <c r="G5">
+      <c r="E5">
         <f>50*283.36/1000</f>
         <v>14.167999999999999</v>
       </c>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="G5">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
+        <v>11</v>
+      </c>
+      <c r="B6" t="s">
         <v>15</v>
       </c>
-      <c r="B6" t="s">
-        <v>19</v>
-      </c>
-      <c r="C6" t="s">
-        <v>4</v>
-      </c>
-      <c r="D6" t="s">
-        <v>6</v>
-      </c>
-      <c r="E6">
+      <c r="C6">
         <v>19.899999999999999</v>
       </c>
-      <c r="F6">
+      <c r="D6">
         <f>Tableau13[[#This Row],[Energie nom totale (kWh)]]</f>
         <v>19.899999999999999</v>
       </c>
-      <c r="G6">
+      <c r="E6">
         <f>50*354.2/1000</f>
         <v>17.71</v>
       </c>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="G6">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="B7" t="s">
-        <v>22</v>
-      </c>
-      <c r="C7" t="s">
-        <v>4</v>
-      </c>
-      <c r="D7" t="s">
-        <v>6</v>
+        <v>29</v>
+      </c>
+      <c r="C7">
+        <v>5</v>
+      </c>
+      <c r="D7" s="1">
+        <f>Tableau13[[#This Row],[Energie nom totale (kWh)]]*Tableau13[[#This Row],[Rendement]]/100</f>
+        <v>4.9349999999999996</v>
       </c>
       <c r="E7">
+        <v>3.5</v>
+      </c>
+      <c r="F7">
+        <v>98.7</v>
+      </c>
+      <c r="G7">
         <v>5</v>
       </c>
-      <c r="F7">
-        <v>5</v>
-      </c>
-      <c r="G7">
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>16</v>
+      </c>
+      <c r="B8" t="s">
+        <v>28</v>
+      </c>
+      <c r="C8">
+        <v>6.9</v>
+      </c>
+      <c r="D8" s="1">
+        <f>Tableau13[[#This Row],[Energie nom totale (kWh)]]*Tableau13[[#This Row],[Rendement]]/100</f>
+        <v>6.8103000000000007</v>
+      </c>
+      <c r="E8">
         <v>3.5</v>
       </c>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>20</v>
-      </c>
-      <c r="B8" t="s">
+      <c r="F8">
+        <v>98.7</v>
+      </c>
+      <c r="G8">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>16</v>
+      </c>
+      <c r="B9" t="s">
+        <v>31</v>
+      </c>
+      <c r="C9">
+        <v>10</v>
+      </c>
+      <c r="D9" s="1">
+        <f>Tableau13[[#This Row],[Energie nom totale (kWh)]]*Tableau13[[#This Row],[Rendement]]/100</f>
+        <v>9.8699999999999992</v>
+      </c>
+      <c r="E9">
+        <v>7</v>
+      </c>
+      <c r="F9">
+        <v>98.7</v>
+      </c>
+      <c r="G9">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>16</v>
+      </c>
+      <c r="B10" t="s">
+        <v>30</v>
+      </c>
+      <c r="C10">
+        <v>11.9</v>
+      </c>
+      <c r="D10" s="1">
+        <f>Tableau13[[#This Row],[Energie nom totale (kWh)]]*Tableau13[[#This Row],[Rendement]]/100</f>
+        <v>11.7453</v>
+      </c>
+      <c r="E10">
+        <v>7</v>
+      </c>
+      <c r="F10">
+        <v>98.7</v>
+      </c>
+      <c r="G10">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>16</v>
+      </c>
+      <c r="B11" t="s">
+        <v>32</v>
+      </c>
+      <c r="C11">
+        <v>13.8</v>
+      </c>
+      <c r="D11" s="1">
+        <f>Tableau13[[#This Row],[Energie nom totale (kWh)]]*Tableau13[[#This Row],[Rendement]]/100</f>
+        <v>13.620600000000001</v>
+      </c>
+      <c r="E11">
+        <v>7</v>
+      </c>
+      <c r="F11">
+        <v>98.7</v>
+      </c>
+      <c r="G11">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>16</v>
+      </c>
+      <c r="B12" t="s">
+        <v>33</v>
+      </c>
+      <c r="C12">
+        <v>15</v>
+      </c>
+      <c r="D12" s="1">
+        <f>Tableau13[[#This Row],[Energie nom totale (kWh)]]*Tableau13[[#This Row],[Rendement]]/100</f>
+        <v>14.805</v>
+      </c>
+      <c r="E12">
+        <v>10.5</v>
+      </c>
+      <c r="F12">
+        <v>98.7</v>
+      </c>
+      <c r="G12">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>16</v>
+      </c>
+      <c r="B13" t="s">
+        <v>34</v>
+      </c>
+      <c r="C13">
+        <v>16.899999999999999</v>
+      </c>
+      <c r="D13" s="1">
+        <f>Tableau13[[#This Row],[Energie nom totale (kWh)]]*F14/100</f>
+        <v>16.680299999999999</v>
+      </c>
+      <c r="E13">
+        <v>10.5</v>
+      </c>
+      <c r="F13">
+        <v>98.7</v>
+      </c>
+      <c r="G13">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>16</v>
+      </c>
+      <c r="B14" t="s">
+        <v>36</v>
+      </c>
+      <c r="C14">
+        <v>18.8</v>
+      </c>
+      <c r="D14" s="1">
+        <f>Tableau13[[#This Row],[Energie nom totale (kWh)]]*F15/100</f>
+        <v>18.555600000000002</v>
+      </c>
+      <c r="E14">
+        <v>10.5</v>
+      </c>
+      <c r="F14">
+        <v>98.7</v>
+      </c>
+      <c r="G14">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>16</v>
+      </c>
+      <c r="B15" t="s">
+        <v>35</v>
+      </c>
+      <c r="C15">
+        <v>20.7</v>
+      </c>
+      <c r="D15" s="1">
+        <f>Tableau13[[#This Row],[Energie nom totale (kWh)]]*F15/100</f>
+        <v>20.430899999999998</v>
+      </c>
+      <c r="E15">
+        <v>10.5</v>
+      </c>
+      <c r="F15">
+        <v>98.7</v>
+      </c>
+      <c r="G15">
         <v>21</v>
       </c>
-      <c r="C8" t="s">
-        <v>4</v>
-      </c>
-      <c r="D8" t="s">
-        <v>6</v>
-      </c>
-      <c r="E8">
-        <v>6.9</v>
-      </c>
-      <c r="F8">
-        <v>6.9</v>
-      </c>
-      <c r="G8">
-        <v>3.5</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>20</v>
-      </c>
-      <c r="B9" t="s">
-        <v>23</v>
-      </c>
-      <c r="C9" t="s">
-        <v>4</v>
-      </c>
-      <c r="D9" t="s">
-        <v>6</v>
-      </c>
-      <c r="E9">
-        <v>11.9</v>
-      </c>
-      <c r="F9">
-        <v>11.9</v>
-      </c>
-      <c r="G9">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
-        <v>20</v>
-      </c>
-      <c r="B10" t="s">
-        <v>24</v>
-      </c>
-      <c r="C10" t="s">
-        <v>4</v>
-      </c>
-      <c r="D10" t="s">
-        <v>6</v>
-      </c>
-      <c r="E10">
-        <v>13.8</v>
-      </c>
-      <c r="F10">
-        <v>13.8</v>
-      </c>
-      <c r="G10">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
-        <v>20</v>
-      </c>
-      <c r="B11" t="s">
-        <v>25</v>
-      </c>
-      <c r="C11" t="s">
-        <v>4</v>
-      </c>
-      <c r="D11" t="s">
-        <v>6</v>
-      </c>
-      <c r="E11">
-        <v>15</v>
-      </c>
-      <c r="F11">
-        <v>15</v>
-      </c>
-      <c r="G11">
-        <v>10.5</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
-        <v>20</v>
-      </c>
-      <c r="B12" t="s">
-        <v>26</v>
-      </c>
-      <c r="C12" t="s">
-        <v>4</v>
-      </c>
-      <c r="D12" t="s">
-        <v>6</v>
-      </c>
-      <c r="E12">
-        <v>16.899999999999999</v>
-      </c>
-      <c r="F12">
-        <v>16.899999999999999</v>
-      </c>
-      <c r="G12">
-        <v>10.5</v>
-      </c>
-    </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
-        <v>20</v>
-      </c>
-      <c r="B13" t="s">
-        <v>27</v>
-      </c>
-      <c r="C13" t="s">
-        <v>4</v>
-      </c>
-      <c r="D13" t="s">
-        <v>6</v>
-      </c>
-      <c r="E13">
-        <v>18.8</v>
-      </c>
-      <c r="F13">
-        <v>18.8</v>
-      </c>
-      <c r="G13">
-        <v>10.5</v>
-      </c>
-    </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
-        <v>20</v>
-      </c>
-      <c r="B14" t="s">
-        <v>28</v>
-      </c>
-      <c r="C14" t="s">
-        <v>4</v>
-      </c>
-      <c r="D14" t="s">
-        <v>6</v>
-      </c>
-      <c r="E14">
-        <v>20.7</v>
-      </c>
-      <c r="F14">
-        <v>20.7</v>
-      </c>
-      <c r="G14">
-        <v>10.5</v>
-      </c>
-    </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A15" t="s">
-        <v>54</v>
-      </c>
-      <c r="B15" t="s">
-        <v>42</v>
-      </c>
-      <c r="E15">
-        <v>5</v>
-      </c>
-      <c r="F15" s="1">
-        <f>Tableau13[[#This Row],[Energie nom totale (kWh)]]*Tableau13[[#This Row],[Colonne1]]/100</f>
-        <v>4.9349999999999996</v>
-      </c>
-      <c r="G15">
-        <v>3.5</v>
-      </c>
-      <c r="H15">
-        <v>98.7</v>
-      </c>
-    </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>54</v>
+        <v>9</v>
       </c>
       <c r="B16" t="s">
-        <v>41</v>
+        <v>17</v>
+      </c>
+      <c r="C16">
+        <v>3.28</v>
+      </c>
+      <c r="D16">
+        <v>3.28</v>
       </c>
       <c r="E16">
-        <v>6.9</v>
-      </c>
-      <c r="F16" s="1">
-        <f>Tableau13[[#This Row],[Energie nom totale (kWh)]]*Tableau13[[#This Row],[Colonne1]]/100</f>
-        <v>6.8103000000000007</v>
-      </c>
-      <c r="G16">
-        <v>3.5</v>
-      </c>
-      <c r="H16">
-        <v>98.7</v>
-      </c>
-    </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A17" t="s">
-        <v>54</v>
-      </c>
-      <c r="B17" t="s">
-        <v>44</v>
-      </c>
-      <c r="E17">
-        <v>10</v>
-      </c>
-      <c r="F17" s="1">
-        <f>Tableau13[[#This Row],[Energie nom totale (kWh)]]*Tableau13[[#This Row],[Colonne1]]/100</f>
-        <v>9.8699999999999992</v>
-      </c>
-      <c r="G17">
-        <v>7</v>
-      </c>
-      <c r="H17">
-        <v>98.7</v>
-      </c>
-    </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A18" t="s">
-        <v>54</v>
-      </c>
-      <c r="B18" t="s">
-        <v>43</v>
-      </c>
-      <c r="E18">
-        <v>11.9</v>
-      </c>
-      <c r="F18" s="1">
-        <f>Tableau13[[#This Row],[Energie nom totale (kWh)]]*Tableau13[[#This Row],[Colonne1]]/100</f>
-        <v>11.7453</v>
-      </c>
-      <c r="G18">
-        <v>7</v>
-      </c>
-      <c r="H18">
-        <v>98.7</v>
-      </c>
-    </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A19" t="s">
-        <v>54</v>
-      </c>
-      <c r="B19" t="s">
-        <v>45</v>
-      </c>
-      <c r="E19">
-        <v>13.8</v>
-      </c>
-      <c r="F19" s="1">
-        <f>Tableau13[[#This Row],[Energie nom totale (kWh)]]*Tableau13[[#This Row],[Colonne1]]/100</f>
-        <v>13.620600000000001</v>
-      </c>
-      <c r="G19">
-        <v>7</v>
-      </c>
-      <c r="H19">
-        <v>98.7</v>
-      </c>
-    </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A20" t="s">
-        <v>54</v>
-      </c>
-      <c r="B20" t="s">
-        <v>46</v>
-      </c>
-      <c r="E20">
-        <v>15</v>
-      </c>
-      <c r="F20" s="1">
-        <f>Tableau13[[#This Row],[Energie nom totale (kWh)]]*Tableau13[[#This Row],[Colonne1]]/100</f>
-        <v>14.805</v>
-      </c>
-      <c r="G20">
-        <v>10.5</v>
-      </c>
-      <c r="H20">
-        <v>98.7</v>
-      </c>
-    </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A21" t="s">
-        <v>54</v>
-      </c>
-      <c r="B21" t="s">
-        <v>47</v>
-      </c>
-      <c r="E21">
-        <v>16.899999999999999</v>
-      </c>
-      <c r="F21" s="1">
-        <f>Tableau13[[#This Row],[Energie nom totale (kWh)]]*H22/100</f>
-        <v>16.680299999999999</v>
-      </c>
-      <c r="G21">
-        <v>10.5</v>
-      </c>
-      <c r="H21">
-        <v>98.7</v>
-      </c>
-    </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A22" t="s">
-        <v>54</v>
-      </c>
-      <c r="B22" t="s">
-        <v>49</v>
-      </c>
-      <c r="E22">
-        <v>18.8</v>
-      </c>
-      <c r="F22" s="1">
-        <f>Tableau13[[#This Row],[Energie nom totale (kWh)]]*H23/100</f>
-        <v>18.555600000000002</v>
-      </c>
-      <c r="G22">
-        <v>10.5</v>
-      </c>
-      <c r="H22">
-        <v>98.7</v>
-      </c>
-    </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A23" t="s">
-        <v>54</v>
-      </c>
-      <c r="B23" t="s">
-        <v>48</v>
-      </c>
-      <c r="E23">
-        <v>20.7</v>
-      </c>
-      <c r="F23" s="1">
-        <f>Tableau13[[#This Row],[Energie nom totale (kWh)]]*H23/100</f>
-        <v>20.430899999999998</v>
-      </c>
-      <c r="G23">
-        <v>10.5</v>
-      </c>
-      <c r="H23">
-        <v>98.7</v>
-      </c>
-    </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A24" t="s">
-        <v>13</v>
-      </c>
-      <c r="B24" t="s">
-        <v>29</v>
-      </c>
-      <c r="C24" t="s">
-        <v>4</v>
-      </c>
-      <c r="D24" t="s">
-        <v>6</v>
-      </c>
-      <c r="E24">
-        <v>3.28</v>
-      </c>
-      <c r="F24">
-        <v>3.28</v>
-      </c>
-      <c r="G24">
         <f>96*36/1000</f>
         <v>3.456</v>
       </c>
-    </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A25" t="s">
-        <v>13</v>
-      </c>
-      <c r="B25" t="s">
-        <v>30</v>
-      </c>
-      <c r="C25" t="s">
-        <v>4</v>
-      </c>
-      <c r="D25" t="s">
-        <v>6</v>
-      </c>
-      <c r="E25">
+      <c r="G16">
+        <v>3.2</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>9</v>
+      </c>
+      <c r="B17" t="s">
+        <v>18</v>
+      </c>
+      <c r="C17">
         <v>6.56</v>
       </c>
-      <c r="F25">
+      <c r="D17">
         <v>6.56</v>
       </c>
-      <c r="G25">
+      <c r="E17">
         <f>192*36/1000</f>
         <v>6.9119999999999999</v>
       </c>
-    </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A26" t="s">
-        <v>13</v>
-      </c>
-      <c r="B26" t="s">
-        <v>31</v>
-      </c>
-      <c r="C26" t="s">
-        <v>4</v>
-      </c>
-      <c r="D26" t="s">
-        <v>6</v>
-      </c>
-      <c r="E26">
+      <c r="G17">
+        <v>6.5</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>9</v>
+      </c>
+      <c r="B18" t="s">
+        <v>19</v>
+      </c>
+      <c r="C18">
         <v>9.84</v>
       </c>
-      <c r="F26">
+      <c r="D18">
         <v>9.84</v>
       </c>
-      <c r="G26">
+      <c r="E18">
         <f>288*36/1000</f>
         <v>10.368</v>
       </c>
-    </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A27" t="s">
-        <v>13</v>
-      </c>
-      <c r="B27" t="s">
-        <v>32</v>
-      </c>
-      <c r="C27" t="s">
-        <v>4</v>
-      </c>
-      <c r="D27" t="s">
-        <v>6</v>
-      </c>
-      <c r="E27">
+      <c r="G18">
+        <v>9.8000000000000007</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>9</v>
+      </c>
+      <c r="B19" t="s">
+        <v>20</v>
+      </c>
+      <c r="C19">
         <v>13.12</v>
       </c>
-      <c r="F27">
+      <c r="D19">
         <v>13.12</v>
       </c>
-      <c r="G27">
+      <c r="E19">
         <f>384*36/1000</f>
         <v>13.824</v>
       </c>
-    </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A28" t="s">
-        <v>13</v>
-      </c>
-      <c r="B28" t="s">
-        <v>33</v>
-      </c>
-      <c r="C28" t="s">
-        <v>4</v>
-      </c>
-      <c r="D28" t="s">
-        <v>6</v>
-      </c>
-      <c r="E28">
+      <c r="G19">
+        <v>13.1</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>9</v>
+      </c>
+      <c r="B20" t="s">
+        <v>21</v>
+      </c>
+      <c r="C20">
         <v>16.399999999999999</v>
       </c>
-      <c r="F28">
+      <c r="D20">
         <v>16.399999999999999</v>
       </c>
-      <c r="G28">
+      <c r="E20">
         <f>480*36/1000</f>
         <v>17.28</v>
       </c>
-    </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A29" t="s">
-        <v>34</v>
-      </c>
-      <c r="B29" t="s">
-        <v>35</v>
-      </c>
-      <c r="C29" t="s">
-        <v>4</v>
-      </c>
-      <c r="D29" t="s">
-        <v>6</v>
-      </c>
-      <c r="E29">
+      <c r="G20">
+        <v>16.399999999999999</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>22</v>
+      </c>
+      <c r="B21" t="s">
+        <v>23</v>
+      </c>
+      <c r="C21">
         <v>9.8000000000000007</v>
       </c>
-      <c r="F29">
+      <c r="D21">
         <v>8.8000000000000007</v>
       </c>
-      <c r="G29">
+      <c r="E21">
         <v>5</v>
       </c>
-    </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A30" t="s">
-        <v>36</v>
-      </c>
-      <c r="B30" t="s">
-        <v>37</v>
-      </c>
-      <c r="C30" t="s">
-        <v>4</v>
-      </c>
-      <c r="D30" t="s">
-        <v>6</v>
-      </c>
-      <c r="E30">
+      <c r="G21">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>24</v>
+      </c>
+      <c r="B22" t="s">
+        <v>25</v>
+      </c>
+      <c r="C22">
         <v>9.1999999999999993</v>
       </c>
-      <c r="F30">
+      <c r="D22">
         <v>9.1999999999999993</v>
       </c>
-      <c r="G30">
+      <c r="E22">
         <v>5</v>
       </c>
-    </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A31" t="s">
-        <v>38</v>
-      </c>
-      <c r="B31" t="s">
-        <v>39</v>
-      </c>
-      <c r="C31" t="s">
-        <v>4</v>
-      </c>
-      <c r="D31" t="s">
-        <v>6</v>
-      </c>
-      <c r="E31">
+      <c r="G22">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>26</v>
+      </c>
+      <c r="B23" t="s">
+        <v>27</v>
+      </c>
+      <c r="C23">
         <v>9.6</v>
       </c>
-      <c r="F31">
+      <c r="D23">
         <v>9.1199999999999992</v>
       </c>
-      <c r="G31">
+      <c r="E23">
         <v>9</v>
       </c>
-    </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A32" t="s">
-        <v>20</v>
-      </c>
-      <c r="B32" t="s">
-        <v>40</v>
-      </c>
-      <c r="C32" t="s">
-        <v>4</v>
-      </c>
-      <c r="D32" t="s">
-        <v>6</v>
-      </c>
-      <c r="E32">
+      <c r="G23">
         <v>10</v>
-      </c>
-      <c r="F32">
-        <v>10</v>
-      </c>
-      <c r="G32">
-        <v>3.5</v>
       </c>
     </row>
   </sheetData>
@@ -1397,30 +1135,30 @@
         <v>2</v>
       </c>
       <c r="C1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D1" t="s">
+        <v>39</v>
+      </c>
+      <c r="E1" t="s">
+        <v>38</v>
+      </c>
+      <c r="F1" t="s">
+        <v>37</v>
+      </c>
+      <c r="G1" t="s">
+        <v>5</v>
+      </c>
+      <c r="H1" t="s">
         <v>7</v>
-      </c>
-      <c r="D1" t="s">
-        <v>52</v>
-      </c>
-      <c r="E1" t="s">
-        <v>51</v>
-      </c>
-      <c r="F1" t="s">
-        <v>50</v>
-      </c>
-      <c r="G1" t="s">
-        <v>9</v>
-      </c>
-      <c r="H1" t="s">
-        <v>11</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="B2" t="s">
-        <v>42</v>
+        <v>29</v>
       </c>
       <c r="C2">
         <v>5</v>
@@ -1436,7 +1174,7 @@
         <v>98.7</v>
       </c>
       <c r="G2" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="H2">
         <v>80</v>
@@ -1444,10 +1182,10 @@
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="B3" t="s">
-        <v>41</v>
+        <v>28</v>
       </c>
       <c r="C3">
         <v>6.9</v>
@@ -1463,7 +1201,7 @@
         <v>98.7</v>
       </c>
       <c r="G3" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="H3">
         <v>80</v>
@@ -1471,10 +1209,10 @@
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="B4" t="s">
-        <v>44</v>
+        <v>31</v>
       </c>
       <c r="C4">
         <v>10</v>
@@ -1490,7 +1228,7 @@
         <v>98.7</v>
       </c>
       <c r="G4" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="H4">
         <v>80</v>
@@ -1498,10 +1236,10 @@
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="B5" t="s">
-        <v>43</v>
+        <v>30</v>
       </c>
       <c r="C5">
         <v>11.9</v>
@@ -1517,7 +1255,7 @@
         <v>98.7</v>
       </c>
       <c r="G5" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="H5">
         <v>80</v>
@@ -1525,10 +1263,10 @@
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="B6" t="s">
-        <v>45</v>
+        <v>32</v>
       </c>
       <c r="C6">
         <v>13.8</v>
@@ -1544,7 +1282,7 @@
         <v>98.7</v>
       </c>
       <c r="G6" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="H6">
         <v>80</v>
@@ -1552,10 +1290,10 @@
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="B7" t="s">
-        <v>46</v>
+        <v>33</v>
       </c>
       <c r="C7">
         <v>15</v>
@@ -1571,7 +1309,7 @@
         <v>98.7</v>
       </c>
       <c r="G7" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="H7">
         <v>80</v>
@@ -1579,10 +1317,10 @@
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="B8" t="s">
-        <v>47</v>
+        <v>34</v>
       </c>
       <c r="C8">
         <v>16.899999999999999</v>
@@ -1598,7 +1336,7 @@
         <v>98.7</v>
       </c>
       <c r="G8" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="H8">
         <v>80</v>
@@ -1606,7 +1344,7 @@
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B9" t="s">
-        <v>49</v>
+        <v>36</v>
       </c>
       <c r="C9">
         <v>18.8</v>
@@ -1622,7 +1360,7 @@
         <v>98.7</v>
       </c>
       <c r="G9" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="H9">
         <v>80</v>
@@ -1630,10 +1368,10 @@
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="B10" t="s">
-        <v>48</v>
+        <v>35</v>
       </c>
       <c r="C10">
         <v>20.7</v>
@@ -1649,7 +1387,7 @@
         <v>98.7</v>
       </c>
       <c r="G10" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="H10">
         <v>80</v>

--- a/batteries.xlsx
+++ b/batteries.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\technicien_knx\Documents\Antoine_Collignon\Simulateur\Application\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6BB34F87-5EE5-4CE6-BB46-8337FE01568B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3765D881-CD2C-4C86-A125-6803A308E796}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="165" windowWidth="29040" windowHeight="15720" xr2:uid="{439F2F0B-EBB6-48D7-BDE1-24F1D6BB5D52}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{439F2F0B-EBB6-48D7-BDE1-24F1D6BB5D52}"/>
   </bookViews>
   <sheets>
     <sheet name="Batt" sheetId="3" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="85" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="93" uniqueCount="47">
   <si>
     <t>Marque</t>
   </si>
@@ -163,6 +163,21 @@
   </si>
   <si>
     <t>Rendement</t>
+  </si>
+  <si>
+    <t>US5000-48V 3x</t>
+  </si>
+  <si>
+    <t>US5000-48V 4x</t>
+  </si>
+  <si>
+    <t>US5000-48V  2x</t>
+  </si>
+  <si>
+    <t>US5000-48V 1x</t>
+  </si>
+  <si>
+    <t>Pylontech</t>
   </si>
 </sst>
 </file>
@@ -584,7 +599,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{38952B00-7C12-4340-981B-DAC64C55AA63}">
-  <dimension ref="A1:G23"/>
+  <dimension ref="A1:G27"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="22.5703125" bestFit="1" customWidth="1"/>
@@ -1102,6 +1117,90 @@
       </c>
       <c r="G23">
         <v>10</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>46</v>
+      </c>
+      <c r="B24" t="s">
+        <v>45</v>
+      </c>
+      <c r="C24">
+        <v>4.8</v>
+      </c>
+      <c r="D24">
+        <v>4.8</v>
+      </c>
+      <c r="E24">
+        <v>3.5</v>
+      </c>
+      <c r="G24">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>46</v>
+      </c>
+      <c r="B25" t="s">
+        <v>44</v>
+      </c>
+      <c r="C25">
+        <v>9.6</v>
+      </c>
+      <c r="D25">
+        <v>9.6</v>
+      </c>
+      <c r="E25">
+        <v>7</v>
+      </c>
+      <c r="G25">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>46</v>
+      </c>
+      <c r="B26" t="s">
+        <v>42</v>
+      </c>
+      <c r="C26">
+        <f>C25+C24</f>
+        <v>14.399999999999999</v>
+      </c>
+      <c r="D26">
+        <f>Tableau13[[#This Row],[Energie nom totale (kWh)]]</f>
+        <v>14.399999999999999</v>
+      </c>
+      <c r="E26">
+        <v>10.5</v>
+      </c>
+      <c r="G26">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>46</v>
+      </c>
+      <c r="B27" t="s">
+        <v>43</v>
+      </c>
+      <c r="C27">
+        <f>C26+C24</f>
+        <v>19.2</v>
+      </c>
+      <c r="D27">
+        <f>Tableau13[[#This Row],[Energie nom totale (kWh)]]</f>
+        <v>19.2</v>
+      </c>
+      <c r="E27">
+        <v>10.5</v>
+      </c>
+      <c r="G27">
+        <v>20</v>
       </c>
     </row>
   </sheetData>
